--- a/AAII_Financials/Quarterly/BGAOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BGAOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>BGAOY</t>
   </si>
@@ -656,76 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
-      </c>
-      <c r="K7" s="2">
-        <v>45199</v>
       </c>
       <c r="L7" s="2">
         <v>45199</v>
       </c>
       <c r="M7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,8 +769,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +813,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +963,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1007,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,8 +1068,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1083,8 +1110,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1124,8 +1154,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +1174,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,8 +1216,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1223,8 +1260,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1264,8 +1304,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1305,8 +1348,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,8 +1436,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1428,8 +1480,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1469,8 +1524,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,8 +1700,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1674,8 +1744,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1715,8 +1788,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,8 +1832,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1797,54 +1876,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
-      </c>
-      <c r="K38" s="2">
-        <v>45199</v>
       </c>
       <c r="L38" s="2">
         <v>45199</v>
       </c>
       <c r="M38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,70 +1963,74 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>427300</v>
+      </c>
+      <c r="E41" s="3">
         <v>663400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1148600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>514500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>297800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>208900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1376600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>791400</v>
-      </c>
-      <c r="K41" s="3">
-        <v>193700</v>
       </c>
       <c r="L41" s="3">
         <v>193700</v>
       </c>
       <c r="M41" s="3">
+        <v>193700</v>
+      </c>
+      <c r="N41" s="3">
         <v>278400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>256400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>319500</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E42" s="3">
         <v>128000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>50500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>112800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>39000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>41800</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -1959,295 +2049,319 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1472600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1534600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1417500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1374900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1371800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1382200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1235300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1205900</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1208700</v>
       </c>
       <c r="L43" s="3">
         <v>1208700</v>
       </c>
       <c r="M43" s="3">
+        <v>1208700</v>
+      </c>
+      <c r="N43" s="3">
         <v>1222700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1184300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1218300</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>172500</v>
+      </c>
+      <c r="E44" s="3">
         <v>138500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>184400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>152200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>191800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>173600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>199600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>175700</v>
-      </c>
-      <c r="K44" s="3">
-        <v>199000</v>
       </c>
       <c r="L44" s="3">
         <v>199000</v>
       </c>
       <c r="M44" s="3">
+        <v>199000</v>
+      </c>
+      <c r="N44" s="3">
         <v>212900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>219500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>199900</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>275300</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
         <v>402800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>99400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>538700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>452200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>387300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>110500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>451900</v>
       </c>
       <c r="L45" s="3">
         <v>451900</v>
       </c>
       <c r="M45" s="3">
+        <v>451900</v>
+      </c>
+      <c r="N45" s="3">
         <v>452000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>473700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>238300</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2424300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2650000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3203800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2441200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2439200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2258700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3198800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2453900</v>
-      </c>
-      <c r="K46" s="3">
-        <v>2053300</v>
       </c>
       <c r="L46" s="3">
         <v>2053300</v>
       </c>
       <c r="M46" s="3">
+        <v>2053300</v>
+      </c>
+      <c r="N46" s="3">
         <v>2165900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2133900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2086100</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E47" s="3">
         <v>261800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>23500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>142900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>30100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>92100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>97100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>126000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>213800</v>
       </c>
       <c r="L47" s="3">
         <v>213800</v>
       </c>
       <c r="M47" s="3">
+        <v>213800</v>
+      </c>
+      <c r="N47" s="3">
         <v>141900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>140200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>64100</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6761100</v>
+      </c>
+      <c r="E48" s="3">
         <v>6211100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6034100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5230400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5467300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4562300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4516100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4577200</v>
-      </c>
-      <c r="K48" s="3">
-        <v>4227300</v>
       </c>
       <c r="L48" s="3">
         <v>4227300</v>
       </c>
       <c r="M48" s="3">
+        <v>4227300</v>
+      </c>
+      <c r="N48" s="3">
         <v>4276200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4185100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4069700</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5447300</v>
+      </c>
+      <c r="E49" s="3">
         <v>5545400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5938900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5539900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5923500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5526600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4614300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4746300</v>
-      </c>
-      <c r="K49" s="3">
-        <v>4548100</v>
       </c>
       <c r="L49" s="3">
         <v>4548100</v>
       </c>
       <c r="M49" s="3">
+        <v>4548100</v>
+      </c>
+      <c r="N49" s="3">
         <v>4720500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4744700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4674600</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,49 +2445,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>524400</v>
+      </c>
+      <c r="E52" s="3">
         <v>416800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>466200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>309600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>364700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>365400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>298800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>286300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>143900</v>
       </c>
       <c r="L52" s="3">
         <v>143900</v>
       </c>
       <c r="M52" s="3">
+        <v>143900</v>
+      </c>
+      <c r="N52" s="3">
         <v>151700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>152100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>239400</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15310200</v>
+      </c>
+      <c r="E54" s="3">
         <v>15224800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15802700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13797500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14355300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12933700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12856800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12327800</v>
-      </c>
-      <c r="K54" s="3">
-        <v>11315600</v>
       </c>
       <c r="L54" s="3">
         <v>11315600</v>
       </c>
       <c r="M54" s="3">
+        <v>11315600</v>
+      </c>
+      <c r="N54" s="3">
         <v>11589500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11490700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11265400</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,254 +2615,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1612000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1679000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1552600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1556100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1519100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1440100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1438100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1584000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1452200</v>
       </c>
       <c r="L57" s="3">
         <v>1452200</v>
       </c>
       <c r="M57" s="3">
+        <v>1452200</v>
+      </c>
+      <c r="N57" s="3">
         <v>1533800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1523300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1584900</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>251300</v>
+      </c>
+      <c r="E58" s="3">
         <v>191400</v>
       </c>
-      <c r="E58" s="3">
-        <v>723400</v>
-      </c>
       <c r="F58" s="3">
+        <v>766900</v>
+      </c>
+      <c r="G58" s="3">
         <v>682300</v>
       </c>
-      <c r="G58" s="3">
-        <v>571000</v>
-      </c>
       <c r="H58" s="3">
-        <v>515400</v>
+        <v>612300</v>
       </c>
       <c r="I58" s="3">
-        <v>754100</v>
+        <v>555000</v>
       </c>
       <c r="J58" s="3">
+        <v>794000</v>
+      </c>
+      <c r="K58" s="3">
         <v>813500</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1003400</v>
       </c>
       <c r="L58" s="3">
         <v>1003400</v>
       </c>
       <c r="M58" s="3">
+        <v>1003400</v>
+      </c>
+      <c r="N58" s="3">
         <v>1151700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>197700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>706400</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>940200</v>
+      </c>
+      <c r="E59" s="3">
         <v>367500</v>
       </c>
-      <c r="E59" s="3">
-        <v>1093400</v>
-      </c>
       <c r="F59" s="3">
+        <v>1049900</v>
+      </c>
+      <c r="G59" s="3">
         <v>480400</v>
       </c>
-      <c r="G59" s="3">
-        <v>1042800</v>
-      </c>
       <c r="H59" s="3">
-        <v>967500</v>
+        <v>1001600</v>
       </c>
       <c r="I59" s="3">
-        <v>1032500</v>
+        <v>927900</v>
       </c>
       <c r="J59" s="3">
+        <v>992600</v>
+      </c>
+      <c r="K59" s="3">
         <v>427800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>909200</v>
       </c>
       <c r="L59" s="3">
         <v>909200</v>
       </c>
       <c r="M59" s="3">
+        <v>909200</v>
+      </c>
+      <c r="N59" s="3">
         <v>847200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>924600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>347300</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2842500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2914200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3406900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3298500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3175300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2965800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3266800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3381200</v>
-      </c>
-      <c r="K60" s="3">
-        <v>3410200</v>
       </c>
       <c r="L60" s="3">
         <v>3410200</v>
       </c>
       <c r="M60" s="3">
+        <v>3410200</v>
+      </c>
+      <c r="N60" s="3">
         <v>3581900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2694500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3208300</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6087100</v>
+      </c>
+      <c r="E61" s="3">
         <v>5831900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5870800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4865900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5245400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4530200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4544200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4506500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2939200</v>
       </c>
       <c r="L61" s="3">
         <v>2939200</v>
       </c>
       <c r="M61" s="3">
+        <v>2939200</v>
+      </c>
+      <c r="N61" s="3">
         <v>3015300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3662500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3072600</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>228500</v>
+      </c>
+      <c r="E62" s="3">
         <v>319400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>285400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>278500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1004900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>907500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>787600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>202300</v>
-      </c>
-      <c r="K62" s="3">
-        <v>823500</v>
       </c>
       <c r="L62" s="3">
         <v>823500</v>
       </c>
       <c r="M62" s="3">
+        <v>823500</v>
+      </c>
+      <c r="N62" s="3">
         <v>866800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>870300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>868900</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9806900</v>
+      </c>
+      <c r="E66" s="3">
         <v>9745200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10319400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9102400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10131600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9098900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9174700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8680200</v>
-      </c>
-      <c r="K66" s="3">
-        <v>7733900</v>
       </c>
       <c r="L66" s="3">
         <v>7733900</v>
       </c>
       <c r="M66" s="3">
+        <v>7733900</v>
+      </c>
+      <c r="N66" s="3">
         <v>8036000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7808600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7729000</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3612500</v>
+      </c>
+      <c r="E72" s="3">
         <v>3522400</v>
       </c>
-      <c r="E72" s="3">
-        <v>3437500</v>
-      </c>
       <c r="F72" s="3">
+        <v>3554900</v>
+      </c>
+      <c r="G72" s="3">
         <v>2854300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3091700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2749400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2732800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2798700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2650300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2756100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2756600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2780300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2635500</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5314700</v>
+      </c>
+      <c r="E76" s="3">
         <v>5289400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5280100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4462200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4016300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3688000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3682200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3647600</v>
-      </c>
-      <c r="K76" s="3">
-        <v>3581700</v>
       </c>
       <c r="L76" s="3">
         <v>3581700</v>
       </c>
       <c r="M76" s="3">
+        <v>3581700</v>
+      </c>
+      <c r="N76" s="3">
         <v>3553500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3682100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3535300</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,54 +3511,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
-      </c>
-      <c r="K80" s="2">
-        <v>45199</v>
       </c>
       <c r="L80" s="2">
         <v>45199</v>
       </c>
       <c r="M80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3409,8 +3604,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +3624,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>356900</v>
+      </c>
+      <c r="E83" s="3">
         <v>337500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>324700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-89500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>312200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>324200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>317300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-63100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>283400</v>
       </c>
       <c r="L83" s="3">
         <v>283400</v>
       </c>
       <c r="M83" s="3">
+        <v>283400</v>
+      </c>
+      <c r="N83" s="3">
         <v>308400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>324400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-56900</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>324500</v>
+      </c>
+      <c r="E89" s="3">
         <v>504900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>416900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>463800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>610100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>334300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>318300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>494100</v>
-      </c>
-      <c r="K89" s="3">
-        <v>516500</v>
       </c>
       <c r="L89" s="3">
         <v>516500</v>
       </c>
       <c r="M89" s="3">
+        <v>516500</v>
+      </c>
+      <c r="N89" s="3">
         <v>367900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>378100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>495900</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +3950,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-348500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-420300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-366400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-436900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-399300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-323600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-426200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-391300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-380000</v>
       </c>
       <c r="L91" s="3">
         <v>-380000</v>
       </c>
       <c r="M91" s="3">
+        <v>-380000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-343900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-461800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-363400</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-422700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-410900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-164400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-441000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-582200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-946100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-427200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-359200</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-445600</v>
       </c>
       <c r="L94" s="3">
         <v>-445600</v>
       </c>
       <c r="M94" s="3">
+        <v>-445600</v>
+      </c>
+      <c r="N94" s="3">
         <v>-370100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-461800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-360200</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,49 +4144,53 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>110800</v>
+      </c>
+      <c r="E96" s="3">
         <v>152600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>69300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>138700</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>242200</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>178000</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
         <v>246700</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>172100</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,75 +4318,81 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-147400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-185500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>187900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>211200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>58000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-547500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>713100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>454300</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-146100</v>
       </c>
       <c r="L100" s="3">
         <v>-146100</v>
       </c>
       <c r="M100" s="3">
+        <v>-146100</v>
+      </c>
+      <c r="N100" s="3">
         <v>24000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>15200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-27800</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-3300</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K101" s="3">
         <v>-2100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>1000</v>
       </c>
       <c r="L101" s="3">
         <v>1000</v>
@@ -4152,50 +4401,56 @@
         <v>1000</v>
       </c>
       <c r="N101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O101" s="3">
         <v>1100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-245600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-91600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>433400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>238100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>82500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1159300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>605200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>588000</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-75100</v>
       </c>
       <c r="L102" s="3">
         <v>-75100</v>
       </c>
       <c r="M102" s="3">
+        <v>-75100</v>
+      </c>
+      <c r="N102" s="3">
         <v>21800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-68400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>105800</v>
       </c>
     </row>
